--- a/src/test/resources/loginPage.xlsx
+++ b/src/test/resources/loginPage.xlsx
@@ -1,10 +1,11 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <fileVersion appName="xl" lastEdited="5" lowestEdited="4" rupBuild="9302"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="29426"/>
   <workbookPr filterPrivacy="1" defaultThemeVersion="124226"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{831D349B-411A-4E1A-B0C6-B36E4F49522F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="240" yWindow="105" windowWidth="14805" windowHeight="8010"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="General_Data" sheetId="1" r:id="rId1"/>
@@ -16,7 +17,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="16" uniqueCount="14">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="20" uniqueCount="18">
   <si>
     <t>TestCases</t>
   </si>
@@ -58,19 +59,37 @@
   </si>
   <si>
     <t>14thAugust1990</t>
+  </si>
+  <si>
+    <t>TC1_Verify_Excel_Data2</t>
+  </si>
+  <si>
+    <t>Puja</t>
+  </si>
+  <si>
+    <t>Dutta</t>
+  </si>
+  <si>
+    <t>16thFeb1992</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <fonts count="1" x14ac:knownFonts="1">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <fonts count="2" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color rgb="FF000000"/>
+      <name val="Consolas"/>
+      <family val="3"/>
     </font>
   </fonts>
   <fills count="2">
@@ -93,9 +112,10 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -106,14 +126,17 @@
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
       <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
     </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
+    </ext>
   </extLst>
 </styleSheet>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme 2007 - 2010">
   <a:themeElements>
-    <a:clrScheme name="Office">
+    <a:clrScheme name="Office 2007 - 2010">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -151,7 +174,7 @@
         <a:srgbClr val="800080"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office">
+    <a:fontScheme name="Office 2007 - 2010">
       <a:majorFont>
         <a:latin typeface="Cambria"/>
         <a:ea typeface=""/>
@@ -223,7 +246,7 @@
         <a:font script="Geor" typeface="Sylfaen"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office">
+    <a:fmtScheme name="Office 2007 - 2010">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -396,16 +419,16 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:D3"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+  <dimension ref="A1:D4"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="21.5703125" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="11.140625" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="15.140625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="21.54296875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="11.1796875" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="15.1796875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -419,7 +442,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="3" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
         <v>4</v>
       </c>
@@ -431,6 +454,62 @@
       </c>
       <c r="D3" s="1" t="s">
         <v>13</v>
+      </c>
+    </row>
+    <row r="4" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A4" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="B4" t="s">
+        <v>15</v>
+      </c>
+      <c r="C4" t="s">
+        <v>16</v>
+      </c>
+      <c r="D4" t="s">
+        <v>17</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
+  <dimension ref="A1:D3"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <cols>
+    <col min="1" max="1" width="21.54296875" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="3" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A3" t="s">
+        <v>4</v>
+      </c>
+      <c r="B3" t="s">
+        <v>5</v>
+      </c>
+      <c r="C3" t="s">
+        <v>7</v>
+      </c>
+      <c r="D3" t="s">
+        <v>6</v>
       </c>
     </row>
   </sheetData>
@@ -438,51 +517,10 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:D3"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
-  <cols>
-    <col min="1" max="1" width="21.5703125" bestFit="1" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" t="s">
-        <v>1</v>
-      </c>
-      <c r="C1" t="s">
-        <v>2</v>
-      </c>
-      <c r="D1" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="3" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A3" t="s">
-        <v>4</v>
-      </c>
-      <c r="B3" t="s">
-        <v>5</v>
-      </c>
-      <c r="C3" t="s">
-        <v>7</v>
-      </c>
-      <c r="D3" t="s">
-        <v>6</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <dimension ref="A1"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <sheetData/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
